--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>44489</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>45922</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45289</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44732</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45923</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46258</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>46268</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45275</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>46283</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44942</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>44845</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45607</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45328</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45750</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46203</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>46248</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>46276</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>45414</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>46239</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45665</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45545</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>45923</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45986</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45687</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45364</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>46178</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>44959</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>46120</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44869</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>46199</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>46213</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>46218</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>45075</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>45195</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45667</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>45726</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>45804</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>45831</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44467</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44664</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44460</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44746</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44726</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44505</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44651</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>44719</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44606</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44713</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44482</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44783</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44854</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>44799</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44694</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44494</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44651</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44518</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44511</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>44655</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44482</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44598</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44980</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44805</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45617</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45674</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44637</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45090</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45218</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44963</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45159</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45418</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45578</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44743</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>45167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>45742</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>45771</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45471</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45393</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>44876</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44889</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45223</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45750</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45223</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44963</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45567</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45453</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>45587</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>45544</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>45153</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>45208</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45177</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44935</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45686</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44867</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45063</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45245</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>44544</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>45643</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45106</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45720</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>45107</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44788</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45427</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>45638</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45114</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45712</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45700</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45896</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45245</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45180</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45072</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45072</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>46136</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45420</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>45271</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45169</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45841</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>45790</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>45901</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>45664</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45835</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>46136</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>46136</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45789</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45769</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45246</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45902</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45841</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45891</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45819</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45909</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>46140</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45671</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45939</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45299</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45834</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>46140</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45911</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45407</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46108</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45867</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>46141</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45456</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45880</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45775</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45665</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45124</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>46141</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45267</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44508</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45925</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45924</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45744</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45929</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>45253</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45628</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45408</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>45931</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>45931</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>46142</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>46142</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45087</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45088</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>45932</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45933</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>45750</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45167</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>44911</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>46148</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45257</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45093</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>46153</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>46153</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>46153</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45951</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>46153</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45436</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>45418</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45953</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>46153</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>46153</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46153</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45954</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>46153</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>46153</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>46153</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>46153</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45959</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>46153</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45959</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>46153</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45229</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45393</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>45012</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45960</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45965</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>45965</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45428</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>46153</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44803</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45968</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45968</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45364</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45658</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45971</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45971</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45973</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45973</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45973</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45973</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45973</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45973</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45973</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45972</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45401</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45618</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45384</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45974</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45974</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45974</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45974</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45978</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45229</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>45484</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45327</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>46155</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>45740</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45981</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>45982</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21701,7 +21701,7 @@
         <v>45985</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45985</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45222</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45988</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45989</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45989</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45989</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45989</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45992</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45602</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45992</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45992</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45588</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>46163</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>46163</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45391</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44536</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>44579</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>46163</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>46163</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>46163</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>45077</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46163</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>46163</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>44911</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>45995</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45995</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45995</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>46167</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45996</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>46167</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>46000</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>46167</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>46001</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>46000</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>46167</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>46001</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46001</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>46001</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>46167</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>46001</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>46001</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>46003</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>46003</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>46001</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>46167</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>46167</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46167</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>46002</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>46002</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45037</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>44789</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>46167</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>46002</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>44805</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46167</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>46006</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45202</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>46006</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>45232</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26359,7 +26359,7 @@
         <v>46167</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>46004</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>46167</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46167</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45133</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>46004</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>45456</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>44470</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>46010</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>46169</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>46014</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>46169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>46169</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>44847</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45940</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45229</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45758</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>46170</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
         <v>46170</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>46170</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45077</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>44960</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>45484</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>46170</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>44588</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>46170</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>46170</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>46170</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>46174</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45986</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45063</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44981</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45203</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>45463</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>44579</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>46040</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>46174</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45749</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>46171</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>45835</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>46175</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45578</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>46175</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45120</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>45240</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>46178</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>46178</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45202</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>46056</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         <v>46056</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>46059</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45418</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44994</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>46064</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>46182</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>46182</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         <v>46182</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45616</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>46182</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30846,7 +30846,7 @@
         <v>46182</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>46182</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>46181</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>44887</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45173</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>46181</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>46076</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>46183</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>46178</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45014</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>46183</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>44957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>46188</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>46187</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45474</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46185</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>46087</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45511</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44596</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>46188</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>45186</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>46186</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>46190</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>46092</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32698,7 +32698,7 @@
         <v>46092</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>46094</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>46094</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>45569</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>46094</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>45114</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>45244</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>46094</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>46094</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45583</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         <v>46191</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>46098</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>46098</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>44691</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>46099</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>46191</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>46100</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45947</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>46195</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>46195</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45096</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45195</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>46106</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>46106</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>46106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>46105</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>46108</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>46107</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>46197</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>45655</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45655</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>46197</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>46107</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>46107</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>46108</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>46108</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44935</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>46114</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>46202</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45230</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>46119</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>46119</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>46119</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>46120</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>46122</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>46122</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>46122</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>46122</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>46125</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>46244</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45274</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>46126</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>46129</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>46127</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>46245</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>46245</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>46129</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>46127</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>46199</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45152</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>44951</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>46244</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>46244</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>46127</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>46127</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>45184</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>46128</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>46127</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>46202</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>46244</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>46127</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>46204</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>46133</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>46203</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>46203</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>46090</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>46133</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45124</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46247</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45524</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>46135</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>46134</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>46134</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>46134</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>45579</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>45568</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>46203</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>46199</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45964</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>45342</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>45882</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>44896</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>46203</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46247</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>46246</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>46251</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>46251</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>46205</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>46205</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46251</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>46206</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>46205</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>46251</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>46251</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>46252</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>46210</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45567</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45700</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>46252</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>46213</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45088</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>46255</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>44530</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>46255</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>45439</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>46254</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44960</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>46212</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>46259</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45436</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>46259</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>44880</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45700</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45204</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>44467</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45720</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>46218</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>46261</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>46261</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>46261</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>46261</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>44461</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>44872</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45516</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>46189</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>44809</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>46223</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44672</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>46264</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>46265</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>46264</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44998</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>46223</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>46265</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>46219</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45741</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43866,7 +43866,7 @@
         <v>46266</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>46266</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>46267</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>46266</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>46266</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>46268</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>46269</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>46269</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>46269</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>46269</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>46225</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>46226</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>46226</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>46226</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>46227</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>46272</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>46227</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45471</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>46273</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>46272</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>46272</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45414</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>46272</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>46272</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45586</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>46186</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45495</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45439</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>46232</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>46274</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>46231</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>46232</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>46232</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>46233</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>46276</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>46279</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>46234</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>46269</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>46233</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>44515</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>46237</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>46237</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>46233</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>46281</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45477</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>45530</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>45791</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45593</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45790</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45667</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45793</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45792</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>45792</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>46240</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>46283</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>46282</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>45355</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48267,7 +48267,7 @@
         <v>44543</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45747</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>46239</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>44515</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>46239</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>46240</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>45796</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>46239</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45439</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>46241</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>45322</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>45747</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>46283</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>44801</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>45586</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>46240</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>46240</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45805</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45805</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>45810</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45470</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45469</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45825</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>45825</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45826</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45826</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45827</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45832</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>45835</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>45834</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50532,7 +50532,7 @@
         <v>45827</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45688</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45841</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50761,7 +50761,7 @@
         <v>45826</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>45870</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>45882</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>44438</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>44328</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51146,7 +51146,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45246</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>45247</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45247</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45247</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45247</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>44991</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51687,7 +51687,7 @@
         <v>45247</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51765,7 +51765,7 @@
         <v>45233</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>45247</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>45247</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>45687</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45246</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>45716</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45995</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52311,7 +52311,7 @@
         <v>46010</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>46036</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>

--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>44489</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>45922</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45289</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44732</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45923</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46258</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>46268</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>46283</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44942</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>44845</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45607</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>46203</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45328</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46276</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>46239</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>46248</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45750</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>45414</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>45364</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>45726</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45545</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45075</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45923</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45804</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>46120</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45986</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>45195</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44684</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45831</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>46199</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>46213</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45665</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>46218</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44869</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>45602</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44959</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45667</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44467</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44664</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44726</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44505</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44651</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44713</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44482</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44783</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44854</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44799</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44694</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44494</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44651</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44518</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44511</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44655</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44482</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44598</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45246</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45203</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44467</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>45700</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45342</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45208</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45391</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45453</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45096</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>45428</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>45223</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45471</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45384</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45408</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44880</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45257</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45418</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45267</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45439</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45322</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44543</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45796</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45758</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>45244</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45463</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45793</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45511</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45355</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44515</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45747</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45120</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>44801</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45474</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45986</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45393</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>46040</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45902</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45674</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45909</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>46056</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>46056</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45586</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>45911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>46059</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>45664</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>46064</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45418</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44672</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>45578</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>45924</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>45240</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>46076</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45925</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44530</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45929</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45931</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45202</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45805</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>45805</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45810</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45470</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45587</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45579</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45933</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>46087</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>44935</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>46092</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>46092</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>46094</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>46094</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>46094</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>46094</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>46094</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>46098</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>46098</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>46100</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45364</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>46099</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>46105</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44788</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>46107</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45951</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45951</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>46106</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>46107</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>46107</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>46106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>46106</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45953</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>46108</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>46108</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>46108</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45954</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>46114</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45617</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>46119</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45567</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45959</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45469</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>46119</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45959</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>46120</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>46122</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>46122</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>46125</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>46127</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45965</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>46127</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>46127</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>46127</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45968</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45968</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>46127</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45971</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45971</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45972</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45973</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45973</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45974</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45974</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45973</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45973</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45973</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>46126</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45152</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45973</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>46129</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>44998</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>46128</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45436</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>46133</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>46134</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>46133</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45982</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>46134</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>46134</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45981</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45985</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>45985</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45988</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>46136</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45569</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>46136</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45989</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45992</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45992</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45992</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>46136</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45989</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45989</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45989</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>46135</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45420</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45896</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45993</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45996</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45995</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45901</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45995</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45995</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45072</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45484</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>46000</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>45790</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>46000</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>46001</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>46001</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>46001</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>46002</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>46140</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>46001</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>46002</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>46001</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>46002</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>46001</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>46001</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>46004</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>46003</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>45819</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>46004</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45789</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46003</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46006</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45720</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>46006</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45232</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45964</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45841</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>46010</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45880</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>46014</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45841</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44579</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>46140</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45771</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45891</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45229</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45826</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>45825</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45825</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>45700</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45835</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>46141</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>45750</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>46141</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>45826</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45775</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45939</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>46142</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45867</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45834</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45012</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>46142</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45456</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45827</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>46108</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45202</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>45832</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>46148</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45014</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45427</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45088</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45167</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45769</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>46153</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>46153</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>46153</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>46153</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>46153</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>46153</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>46153</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45834</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46153</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>46153</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>46153</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>45088</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>46153</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46153</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>46153</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>46153</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>45063</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>46155</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45835</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>45827</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45688</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45077</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45841</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>46163</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>46163</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>46163</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>46163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>46163</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>46163</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45245</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>46167</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45940</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>46167</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>46167</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>46167</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45826</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>46167</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>46167</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>46167</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>46167</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>46167</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>46167</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>46167</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>46167</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45106</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>46167</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>46169</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>46169</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>46169</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45271</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>46170</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>46170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>46170</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>46170</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>46170</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>45741</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>46170</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>46170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>45133</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>46171</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>45835</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>45749</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>44960</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44957</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>46175</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45393</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>44980</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>46174</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45544</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>46175</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>46174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45114</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45870</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>46178</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>45567</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45616</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>46181</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>46178</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45418</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45588</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>46178</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>46182</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>46182</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>46182</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>44637</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>46182</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>46183</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>46182</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45439</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>46181</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>46182</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>46185</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>45671</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>46187</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>46183</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>46186</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>46188</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>45274</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>46188</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>45484</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>46191</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>46190</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>44508</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>46191</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>46195</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>46195</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45665</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45947</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>46197</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>46197</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44536</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44596</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>45618</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45169</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>46199</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>46203</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>46203</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>46202</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>45882</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45658</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>46199</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>46205</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>46203</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46204</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>46203</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45063</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45638</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>46205</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>46090</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>46205</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>46251</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>46251</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>46252</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46213</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>46251</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>46252</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>45229</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>46251</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>46251</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>46206</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>46210</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>45107</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>46255</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>46255</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>46254</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45686</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>44743</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45184</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>46212</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45700</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45093</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45456</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>46259</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>46259</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44691</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>46261</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>46261</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>46219</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>46261</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45159</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>46218</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45180</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>46261</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45222</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>46266</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>46264</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45167</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45186</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>46189</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45750</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>46223</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46265</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>46266</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>46265</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>46264</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46266</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>46223</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>46267</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44803</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>46225</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44789</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>44847</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44805</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>44809</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>46268</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>46226</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>46226</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>46226</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>46227</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>45245</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>46227</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>46272</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>46272</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>46269</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>46272</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>46269</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>46272</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>46269</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>46269</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>46186</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>46231</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>46274</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>46272</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45087</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>46273</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46269</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>46233</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>46232</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>46232</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>46232</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>46233</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>46276</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>46237</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>46234</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45177</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>46279</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>46237</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43078,7 +43078,7 @@
         <v>46233</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>46239</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>46282</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>46239</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>44876</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>46281</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>46239</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>45229</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>46240</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>46240</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>46240</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>46286</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>46283</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>45223</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44165,7 +44165,7 @@
         <v>46241</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>45218</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>44887</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>46240</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>46283</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>44960</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>46283</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44889</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>46244</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>46288</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>44867</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>46245</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>46245</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44911</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45568</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>46129</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45253</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>46244</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>46287</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>46288</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>46244</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>46244</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>46289</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45924,7 +45924,7 @@
         <v>46266</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>46246</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>44994</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46158,7 +46158,7 @@
         <v>45153</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44963</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>46247</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>46290</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>46247</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>44872</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>44544</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45114</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
         <v>44981</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>44470</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>45602</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>44963</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>44805</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45124</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45124</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>44911</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45090</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>44579</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
         <v>45401</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45516</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45655</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45037</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45327</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>45578</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>45583</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>45072</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45655</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45204</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45195</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         <v>44935</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45720</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45173</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45742</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45628</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>45712</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45077</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45643</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45740</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45744</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45436</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>45524</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45299</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>45495</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45471</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>45414</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45439</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>45586</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>44515</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45790</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45791</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>45477</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>45593</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45530</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45792</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45667</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>44438</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>44328</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>45247</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>45246</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45247</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45247</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50849,7 +50849,7 @@
         <v>45247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>44991</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45247</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45233</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51156,7 +51156,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45247</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51312,7 +51312,7 @@
         <v>45687</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>45246</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45716</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51546,7 +51546,7 @@
         <v>45995</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>46010</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>46036</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>

--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>44489</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>45922</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45289</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44732</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45923</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>46006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46258</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>46268</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>46283</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44942</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>44845</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>45607</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>46203</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45328</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>46276</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>46239</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>46248</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45750</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>45414</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>45364</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>45726</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45687</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45545</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45075</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45923</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45804</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>46120</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45986</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>45195</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44684</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45831</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>46178</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>46199</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>46213</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45665</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>46218</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44869</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>45602</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44959</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45667</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44467</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44664</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>44746</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>44726</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44505</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44651</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44713</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44482</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44783</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44854</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44799</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44694</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44494</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44651</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44518</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44511</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44655</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44482</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44598</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45246</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45203</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44467</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>45700</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45342</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45208</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45391</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45453</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45096</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>45428</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>45223</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>45471</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45384</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45408</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44880</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>45257</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45418</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45267</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45439</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45322</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44543</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45796</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45758</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>45244</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45747</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45463</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45793</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45511</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>45355</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44515</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45747</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45120</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>44801</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45474</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45986</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45393</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>46040</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45902</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45674</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45909</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>46056</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>46056</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45586</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>45911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>46059</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>45664</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>46064</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45418</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44672</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>45578</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>45924</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>45240</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>46076</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45925</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44530</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45929</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45931</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45202</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>45805</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>45805</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45810</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45470</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45587</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45579</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45933</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>46087</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>44935</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>46092</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>46092</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>46094</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>46094</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>46094</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>46094</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>46094</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>46098</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>46098</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>46100</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45364</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>46099</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>46105</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44788</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>46107</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45951</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45951</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>46106</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>46107</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>46107</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>46106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>46106</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45953</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>46108</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>46108</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>46108</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45954</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>46114</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45617</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>46119</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45567</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45959</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45469</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>46119</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>45959</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>46120</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>46122</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>46122</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>46125</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>46127</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>45965</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>46127</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>46127</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>46127</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45968</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45968</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>46127</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45971</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45971</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45972</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45973</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45973</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45974</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>45974</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45973</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45973</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45973</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>46126</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45152</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>45973</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>46129</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>44998</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>46128</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45436</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>46133</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>46134</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>46133</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45982</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>46134</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>46134</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45981</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45985</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>45985</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45988</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>46136</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45569</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>46136</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45989</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45992</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45992</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45992</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>46136</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45989</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45989</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45989</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>46135</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45420</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45896</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45993</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45996</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45995</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45901</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45995</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45995</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45072</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45484</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>46000</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>45790</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>46000</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>46001</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>46001</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>46001</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>46002</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>46140</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>46001</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>46002</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>46001</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>46002</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>46001</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>46001</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>46004</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>46003</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>45819</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>46004</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45789</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>46003</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>46006</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45720</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>46006</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45232</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45964</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45841</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>46010</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45880</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>46014</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45841</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44579</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>46140</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45771</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45891</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45229</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45826</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>45825</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45825</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>45700</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45835</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>46141</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>45750</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>46141</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>45826</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45775</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45939</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>46142</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45867</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45834</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45012</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>46142</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45456</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45827</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>46108</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45202</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>45832</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>46148</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45014</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45427</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45088</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45167</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45769</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>46153</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>46153</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>46153</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>46153</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>46153</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>46153</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>46153</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45834</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46153</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>46153</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>46153</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>45088</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>46153</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46153</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>46153</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>46153</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         <v>45063</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>46155</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45835</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>45827</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>45688</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45077</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45841</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>46163</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>46163</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>46163</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>46163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>46163</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>46163</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45245</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>46167</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45940</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>46167</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>46167</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>46167</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45826</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>46167</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>46167</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>46167</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>46167</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>46167</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>46167</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>46167</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>46167</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45106</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>46167</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>46169</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>46169</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>46169</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45271</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>46170</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>46170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>46170</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>46170</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>46170</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>45741</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>46170</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>46170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30808,7 +30808,7 @@
         <v>45133</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>46171</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>45835</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31027,7 +31027,7 @@
         <v>45749</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>44960</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44957</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>46175</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45393</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>44980</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>46174</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45544</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>46175</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>46174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45114</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45870</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>46178</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>45567</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45616</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>46181</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>46178</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45418</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>45588</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>46178</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>46182</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>46182</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>46182</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>44637</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>46182</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>46183</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>46182</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45439</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>46181</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>46182</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>46185</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>45671</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>46187</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>46183</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>46186</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>46188</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>45274</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>46188</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>45484</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>46191</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>46190</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>44508</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>46191</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>46195</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>46195</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45665</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45947</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>46197</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>46197</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>44536</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44596</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>45618</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>45169</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>46199</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35179,7 +35179,7 @@
         <v>46203</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>46203</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>46202</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>45882</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45658</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>46199</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>46205</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>46203</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46204</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>46203</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>45063</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45638</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>46205</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>46090</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>46205</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>46251</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>46251</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>46252</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>46213</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>46251</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>46252</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>45229</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>46251</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>46251</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>46206</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>46210</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>45107</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>46255</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>46255</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>46254</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37562,7 +37562,7 @@
         <v>45686</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>44743</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45184</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>46212</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45700</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45093</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45456</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>46259</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>46259</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>44691</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>46261</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>46261</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>46219</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>46261</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45159</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>46218</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45180</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>46261</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45222</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39014,7 +39014,7 @@
         <v>46266</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>46264</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45167</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45186</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>46189</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45750</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>46223</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46265</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>46266</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>46265</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>46264</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46266</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>46223</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>46267</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>44803</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>46225</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44789</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>44847</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44805</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>44809</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>46268</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>46226</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>46226</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>46226</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>46227</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>45245</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>46227</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>46272</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>46272</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>46269</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>46272</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>46269</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>46272</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>46269</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>46269</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>46186</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>46231</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>46274</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>46272</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>45087</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>46273</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46269</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>46233</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>46232</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>46232</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>46232</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>46233</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>46276</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>46237</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>46234</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45177</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>46279</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>46237</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43078,7 +43078,7 @@
         <v>46233</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>46239</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43234,7 +43234,7 @@
         <v>46282</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>46239</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>44876</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>46281</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>46239</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>45229</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>46240</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>46240</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>46240</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>46286</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>46283</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>45223</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44165,7 +44165,7 @@
         <v>46241</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>45218</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>44887</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>46240</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>46283</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>44960</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>46283</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>44889</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>46244</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>46288</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>44867</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>46245</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>46245</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44911</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45568</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>46129</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45253</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45466,7 +45466,7 @@
         <v>46244</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>46287</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>46288</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45695,7 +45695,7 @@
         <v>46244</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45768,7 +45768,7 @@
         <v>46244</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>46289</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45924,7 +45924,7 @@
         <v>46266</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>46246</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>44994</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46158,7 +46158,7 @@
         <v>45153</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44963</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>46247</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>46290</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>46247</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>44872</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>44544</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45114</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
         <v>44981</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>44470</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>45602</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>44963</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>44805</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45124</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45124</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>44911</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45090</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>44579</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
         <v>45401</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45516</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>45655</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45037</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45327</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>45578</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>45583</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>45072</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>45655</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>45204</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>45195</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         <v>44935</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45720</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45173</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45742</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45628</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>45712</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45077</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45643</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45740</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>45744</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45436</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>45524</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45299</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>45495</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45471</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>45414</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45439</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>45586</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>44515</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45790</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45791</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>45477</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>45593</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45530</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45792</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45667</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>44438</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>44328</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>45247</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>45246</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45247</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45247</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50849,7 +50849,7 @@
         <v>45247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>44991</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45247</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45233</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51156,7 +51156,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45247</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51312,7 +51312,7 @@
         <v>45687</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>45246</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45716</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51546,7 +51546,7 @@
         <v>45995</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>46010</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>46036</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>

--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>44489</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>45922</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45289</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44732</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>46006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45923</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45183</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46258</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>46268</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>46283</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44942</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45414</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45054</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44845</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45328</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45750</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>46203</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46276</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>46248</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>45687</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45602</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45726</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45804</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45923</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>45665</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45986</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>46120</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45545</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>46178</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>46199</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>46218</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45364</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>44959</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44869</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>46213</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>45075</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>45195</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45667</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44664</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44505</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44651</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44713</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44482</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44783</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44854</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44494</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44651</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44518</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44511</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44655</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44482</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44980</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45674</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45617</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44805</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44637</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45090</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45218</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>44963</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45418</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45578</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45159</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>46001</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>46001</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>46003</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>46003</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>46001</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>46002</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>46002</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45742</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>45771</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45477</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45471</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45530</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>46006</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44743</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>46006</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45232</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45791</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>45593</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>46004</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45393</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>46004</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>46010</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45790</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>46014</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>45758</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44876</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>45223</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45750</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>45667</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>45986</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44963</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>45567</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>46040</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45223</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45909</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45793</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45792</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45355</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45911</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44543</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>44515</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45796</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45439</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45453</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45587</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45322</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>45747</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>44801</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>45586</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>45805</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>45805</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45153</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45208</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45925</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45924</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45929</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>46056</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>46056</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>46059</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45177</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45931</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44935</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45686</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45933</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>46064</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44867</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45810</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>46076</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45470</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45063</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44544</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45951</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>45245</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45951</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45953</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>45954</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45469</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45959</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45959</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>46087</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46092</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45643</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>46092</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>46094</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45106</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>46094</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45965</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>46094</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>46094</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>46094</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45968</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45968</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>46098</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>45971</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45971</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>46098</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>45973</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>46099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45973</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>46100</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45973</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45973</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45973</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45973</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45973</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45972</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45720</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>44788</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45427</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45638</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45107</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>46106</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>46106</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>46106</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>46105</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>46108</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>46107</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>46107</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45981</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>46107</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45982</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>46108</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45985</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46108</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45985</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45114</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>46114</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45825</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45712</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45825</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45988</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45989</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45989</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>46119</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45989</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>46119</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>46119</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45700</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>46120</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45989</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>45992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46122</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45826</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>46122</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45992</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45992</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45993</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>46125</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45995</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>46126</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45995</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45995</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45826</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>46129</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>46127</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45827</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45996</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>46000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>46001</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>46127</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>46000</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45152</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44951</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>46127</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45180</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45072</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45072</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>46127</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>46128</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>46127</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>46133</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>46001</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>46001</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>46001</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>46133</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45271</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>46135</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45832</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45169</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>46134</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>46134</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>46134</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45835</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45834</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45664</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45827</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45964</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45688</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45841</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45769</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45896</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45246</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45671</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45299</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>46136</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45665</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45124</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>45420</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45826</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45841</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45790</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45901</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45835</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>46136</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>46136</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>45267</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44508</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45789</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45744</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45628</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45841</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45408</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45891</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45819</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>46140</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45939</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45087</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45088</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>45834</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>46140</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>46108</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45867</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>46141</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>45456</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>45750</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45880</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45167</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45775</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44911</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>46141</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45870</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45257</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45093</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>46142</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28166,7 +28166,7 @@
         <v>46142</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>45436</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>45418</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>46148</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>46153</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>46153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46153</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>46153</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>46153</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>46153</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45229</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>46153</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>46153</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>46153</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45393</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>46153</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>46153</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>46153</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>46153</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45012</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>46153</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46155</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45428</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>44803</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>45364</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45658</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>46163</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>46163</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45401</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45618</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>45384</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>46163</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>46163</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>45077</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>46163</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>46163</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45229</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45484</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45327</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>46167</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>46167</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>46167</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>46167</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>46167</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>46167</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>46167</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46167</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45740</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>46167</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>46167</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46167</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>46167</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>46167</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>45222</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>46169</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>46169</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>46169</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45940</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>46170</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>46170</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>46170</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>46170</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>46170</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>46170</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>46170</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>46174</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>46174</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>45749</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>46171</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>45602</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45835</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45882</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>46175</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>46175</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>46178</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>46178</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45588</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>45391</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>44536</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>44579</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>46182</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>46182</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>46182</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>46182</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>46182</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>46182</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>46181</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44911</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>46181</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>46183</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>46178</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>46183</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>46188</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>46187</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>46185</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>46188</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>46186</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>46190</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45037</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>44789</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44805</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>45202</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>46191</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>45133</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>46191</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45947</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>45456</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>46195</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>46195</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>46197</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>46197</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         <v>44847</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>45229</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>46202</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>46199</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>46202</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46204</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>46203</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>46203</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45077</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>46090</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>44960</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45484</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>46203</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46199</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>46203</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>44588</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>46205</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>46205</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>45063</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>46206</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>44981</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>46205</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>45203</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45463</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44579</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>46210</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46212</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>46259</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46259</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45578</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45120</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>46218</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>46261</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45240</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>46261</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>46261</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>46261</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>46189</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45202</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>46223</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>46264</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46265</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>46264</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>46223</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>46265</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>46219</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45418</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>46266</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>44994</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>46267</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45616</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>46266</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>46266</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>46268</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>46269</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>44887</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>46269</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>46269</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46269</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>46225</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45173</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>46226</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>46226</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>46226</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>46227</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>46272</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>46227</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41845,7 +41845,7 @@
         <v>46273</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>46272</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>46272</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45014</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46272</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>44957</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>46186</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>46232</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>46274</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>46231</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>46232</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>46232</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>46233</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46276</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>46279</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>46234</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>46269</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>46233</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>46237</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>46237</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>46233</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>46281</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45474</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>45511</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>44596</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>45186</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>46240</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>46283</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43999,7 +43999,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>46239</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45569</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45114</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>45244</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>46239</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>46240</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45583</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44613,7 +44613,7 @@
         <v>46239</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>46283</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>44691</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>46240</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>46240</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45096</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>46287</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45195</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>46286</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>46129</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45655</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45655</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45529,7 +45529,7 @@
         <v>46244</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>46244</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>46245</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>46241</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>44935</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>46244</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>46283</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>46289</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>46245</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>46266</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>46288</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>46246</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>46288</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45230</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>46290</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45274</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>46247</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>46247</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>45184</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45124</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>46293</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>46293</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>45524</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>46293</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>46252</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>46251</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45579</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45568</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>46252</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>46251</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45342</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>46294</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>46251</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>46251</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>46251</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>46272</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>46244</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46254</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>46255</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>46213</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>46255</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45567</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45700</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48901,7 +48901,7 @@
         <v>45088</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>44530</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>45439</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>44960</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49208,7 +49208,7 @@
         <v>45436</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>44880</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45700</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>45204</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45720</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>44872</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>45516</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>44809</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>44672</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49870,7 +49870,7 @@
         <v>44998</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45741</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>45471</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45414</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>45586</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
         <v>45495</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45439</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>44515</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>44438</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>44328</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>45247</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>45246</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45247</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51020,7 +51020,7 @@
         <v>45247</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>44991</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51171,7 +51171,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45233</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>45247</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45247</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45687</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>45246</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45716</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51717,7 +51717,7 @@
         <v>45995</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>46010</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51873,7 +51873,7 @@
         <v>46036</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>

--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>44489</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>45922</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45289</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44732</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>46006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>45923</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45183</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46258</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>46268</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>46283</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44942</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45414</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45054</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44845</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>45607</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45328</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45750</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>46203</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46276</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>46248</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>45687</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44684</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45602</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45726</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45804</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45923</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>45665</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45986</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>46120</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45545</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>46178</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>46199</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>46218</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45364</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>44959</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44869</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>46213</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>45075</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>45195</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45667</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44664</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44505</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44651</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>44719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44713</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44482</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44783</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44854</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>44799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44494</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44651</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44518</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>44511</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44655</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44598</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44482</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>44980</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45674</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45617</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44805</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44637</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45090</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45218</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>44963</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45418</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45578</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45159</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>46001</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>46001</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>46003</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>46003</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>46001</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>46002</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>46002</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>45742</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>45771</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45477</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45471</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45530</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>46006</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44743</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>46006</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45232</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45791</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>45593</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>46004</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45393</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>46004</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>46010</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45790</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>46014</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>45758</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44876</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>45223</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45750</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>45667</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>45986</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44963</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>45567</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>46040</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45223</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45909</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45793</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45792</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45355</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45911</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44543</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45747</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>44515</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45796</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45439</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45453</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45587</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45322</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>45747</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>44801</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>45586</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>45805</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>45805</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45153</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45208</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45925</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45924</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45929</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>46056</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>46056</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>46059</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45177</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45931</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44935</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45686</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45933</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>46064</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44867</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45810</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>46076</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45470</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45063</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44544</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45951</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>45245</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45951</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45953</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>45954</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45469</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45959</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45959</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>46087</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>46092</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45643</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>46092</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>46094</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45106</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>46094</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45965</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>46094</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>46094</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>46094</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45968</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45968</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>46098</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>45971</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45971</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>46098</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>45973</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>46099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45973</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>46100</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45973</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45973</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45973</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45973</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45973</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45972</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45720</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>44788</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45427</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45638</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45107</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>46106</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>46106</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>46106</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>46105</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>46108</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>46107</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>46107</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45981</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>46107</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45982</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>46108</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45985</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>46108</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45985</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45114</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>46114</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45825</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45712</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45825</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45988</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45989</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>45989</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>46119</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45989</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>46119</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>46119</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45700</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>46120</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45989</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>45992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46122</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45826</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>46122</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45992</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45992</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45993</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>46125</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45995</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>46126</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>45995</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45995</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45826</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>46129</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>46127</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45827</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45996</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>46000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>46001</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>46127</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>46000</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45152</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44951</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>46127</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45180</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45072</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45072</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>46127</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>46128</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>46127</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>46133</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>46001</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>46001</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>46001</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>46133</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45271</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>46135</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45832</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45169</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>46134</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>46134</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>46134</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45835</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45834</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45664</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45827</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45964</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45688</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45841</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45769</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45896</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45246</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45671</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45299</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>46136</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45665</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45124</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>45420</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45826</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45841</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45790</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45901</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45835</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>46136</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>46136</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>45267</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44508</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45789</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45744</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45628</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45841</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45408</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45891</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45819</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>46140</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45939</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45087</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>45088</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>45834</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>46140</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>46108</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45867</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>46141</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27328,7 +27328,7 @@
         <v>45456</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>45750</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>45880</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45167</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45775</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44911</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>46141</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>45870</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45257</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45093</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>46142</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28166,7 +28166,7 @@
         <v>46142</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>45436</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>45418</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>46148</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>46153</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>46153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46153</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>46153</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>46153</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>46153</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45229</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>46153</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>46153</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>46153</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45393</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>46153</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>46153</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>46153</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>46153</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45012</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>46153</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46155</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45428</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>44803</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>45364</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45658</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>46163</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>46163</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45401</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45618</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30466,7 +30466,7 @@
         <v>45384</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>46163</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>46163</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>45077</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>46163</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>46163</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45229</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45484</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45327</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>46167</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>46167</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>46167</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>46167</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>46167</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>46167</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>46167</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46167</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45740</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>46167</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>46167</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46167</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>46167</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>46167</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>45222</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>46169</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>46169</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>46169</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45940</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>46170</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>46170</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>46170</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>46170</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>46170</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>46170</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>46170</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>46174</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>46174</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>45749</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>46171</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>45602</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45835</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45882</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>46175</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>46175</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>46178</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>46178</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45588</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34092,7 +34092,7 @@
         <v>45391</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>44536</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>44579</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>46182</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>46182</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>46182</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>46182</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>46182</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>46182</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>46181</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>44911</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>46181</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>46183</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>46178</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>46183</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>46188</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>46187</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>46185</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>46188</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>46186</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>46190</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45037</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>44789</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>44805</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>45202</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>46191</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>45133</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>46191</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45947</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>45456</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>46195</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>46195</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>46197</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>46197</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         <v>44847</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>45229</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>46202</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>46199</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>46202</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46204</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>46203</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>46203</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45077</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>46090</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>44960</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45484</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37620,7 +37620,7 @@
         <v>46203</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37698,7 +37698,7 @@
         <v>46199</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>46203</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>44588</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>46205</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>46205</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>45063</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>46206</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>44981</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>46205</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>45203</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>45463</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>44579</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>46210</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46212</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>46259</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46259</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45578</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45120</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>46218</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>46261</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45240</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>46261</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>46261</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>46261</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>46189</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45202</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>46223</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>46264</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46265</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>46264</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>46223</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>46265</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>46219</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45418</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>46266</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>44994</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>46267</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45616</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>46266</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>46266</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>46268</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>46269</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>44887</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>46269</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>46269</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46269</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>46225</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45173</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>46226</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>46226</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>46226</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>46227</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>46272</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>46227</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41845,7 +41845,7 @@
         <v>46273</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>46272</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>46272</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45014</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>46272</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>44957</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>46186</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>46232</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>46274</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>46231</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>46232</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>46232</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42771,7 +42771,7 @@
         <v>46233</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46276</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>46279</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>46234</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>46269</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>46233</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>46237</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>46237</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>46233</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>46281</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45474</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>45511</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>44596</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43770,7 +43770,7 @@
         <v>45186</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>46240</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43921,7 +43921,7 @@
         <v>46283</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43999,7 +43999,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>46239</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45569</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45114</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>45244</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>46239</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>46240</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45583</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44613,7 +44613,7 @@
         <v>46239</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>46283</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>44691</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>46240</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>46240</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45096</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>46287</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45195</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>46286</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>46129</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45655</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45655</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45529,7 +45529,7 @@
         <v>46244</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>46244</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>46245</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>46241</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45836,7 +45836,7 @@
         <v>44935</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>46244</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45987,7 +45987,7 @@
         <v>46283</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>46289</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>46245</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>46266</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>46288</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>46246</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>46288</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45230</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>46290</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45274</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>46247</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>46247</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>45184</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45124</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>46293</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>46293</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>45524</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47293,7 +47293,7 @@
         <v>46293</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>46252</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>46251</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45579</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45568</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>46252</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>46251</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45342</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>46294</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>46251</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>46251</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>46251</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>46272</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>46244</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46254</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>46255</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>46213</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>46255</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45567</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45700</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48901,7 +48901,7 @@
         <v>45088</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>44530</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>45439</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>44960</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49208,7 +49208,7 @@
         <v>45436</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>44880</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45700</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>45204</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45720</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>44872</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>45516</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>44809</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>44672</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49870,7 +49870,7 @@
         <v>44998</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45741</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>45471</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45414</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>45586</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
         <v>45495</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45439</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>44515</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>44438</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>44328</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>45247</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>45246</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45247</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51020,7 +51020,7 @@
         <v>45247</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>44991</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51171,7 +51171,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45233</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>45247</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45247</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45687</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>45246</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45716</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51717,7 +51717,7 @@
         <v>45995</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>46010</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51873,7 +51873,7 @@
         <v>46036</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>

--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>44489</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>45922</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45289</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44732</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>46199</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46268</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>46283</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>46258</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44942</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45750</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>44845</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>45054</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45414</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>45328</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>45607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>46203</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46276</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>46248</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44959</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45364</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45545</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45075</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45667</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45923</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45726</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45804</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45665</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>45831</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45986</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>44684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>46120</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44869</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45687</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>46178</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>46199</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>46218</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>46213</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44664</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44505</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44694</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44494</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44655</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>44651</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44719</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44606</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44511</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44713</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44482</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>44783</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44854</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44651</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44518</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44482</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44598</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45203</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45014</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45342</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45427</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45088</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44579</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45769</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>45401</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45516</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45088</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>45391</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45453</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45096</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>45428</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>45655</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>45230</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45063</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>45037</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45327</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45246</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45208</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>45223</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45471</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45583</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45072</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45408</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45384</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44880</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45700</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>45267</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45245</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45257</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>45418</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>45655</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45204</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>45106</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45195</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44935</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45720</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>45173</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45244</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45271</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>45463</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>45741</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>45133</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>45742</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45628</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45511</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45712</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45077</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>44960</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44957</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45120</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45393</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44980</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45643</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45474</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45740</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>45744</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45436</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45393</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45524</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45114</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45299</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>44588</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45909</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45567</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>45674</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45418</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45588</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45911</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45495</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>44637</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45471</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45414</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45439</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45439</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45586</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45274</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45664</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>45418</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45484</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>45924</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44672</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45578</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44515</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44508</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>45240</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45790</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45791</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45665</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45477</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45593</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45530</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45925</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45792</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45667</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45439</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44530</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45929</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45322</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44543</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44536</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45796</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>44596</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45747</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45202</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45618</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45169</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>45793</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45587</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45355</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44515</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45931</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45747</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45579</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>44801</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45933</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>44935</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45658</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45586</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>45063</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45638</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>45805</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>45364</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45805</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45810</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>45470</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45229</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44788</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45469</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45107</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45617</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45567</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45686</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44743</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45826</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45184</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45825</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45700</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45093</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45825</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45826</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45951</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>45827</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45456</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45832</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45951</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45953</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45954</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45959</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45959</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>44691</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45834</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>44998</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45835</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45827</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45159</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45965</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45180</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>45436</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45688</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45965</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45968</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>45968</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>45841</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45971</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45569</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45971</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45972</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45222</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45973</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45167</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45186</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45974</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45974</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45974</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45973</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45750</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45973</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45973</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45973</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45826</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>44803</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45072</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45484</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>44789</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44847</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44805</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44809</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45245</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45870</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45720</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45087</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44579</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45982</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45771</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>45882</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45981</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>46094</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>46094</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>46098</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>46098</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45229</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>46100</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45177</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>45985</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>46099</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45700</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>46105</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45750</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45985</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>46107</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44876</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45012</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45988</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>46106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>46107</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>46107</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>46106</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46106</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>46108</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>46108</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>46108</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45229</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45989</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>45992</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45992</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45992</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>45202</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>45989</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45989</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45989</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45223</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45218</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>46114</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>46119</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>46119</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>46119</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>44887</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>46120</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45993</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>46122</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>44960</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>46122</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>46125</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45996</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45995</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>46127</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45995</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44889</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>46127</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>44951</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>46127</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45995</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>46000</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>46000</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>46001</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>46001</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>46127</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>46127</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>46001</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>46002</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>46126</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>46001</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45152</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>46002</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>46001</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>46129</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>44867</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>46002</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>44911</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>46128</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45568</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45253</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>46001</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>46001</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>46004</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46133</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>46003</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>46134</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>46133</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>46134</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>46134</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>46004</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>46003</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46006</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46006</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45232</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>46136</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44994</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>46136</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45153</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44963</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>46010</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46136</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>46135</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45420</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45896</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>46014</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45758</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45901</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>44872</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45790</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46140</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45819</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44544</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45789</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45114</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45964</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45841</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45986</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>44981</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>46040</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45880</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>45841</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45602</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>46140</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>44963</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44805</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>45124</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45124</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>44911</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45891</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>45835</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46141</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46141</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>45090</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45775</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45939</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>46142</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>45867</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>45834</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>46056</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>46056</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>46142</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45456</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>46059</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>46108</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>46064</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>46148</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46153</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>46153</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46153</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46153</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>46076</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>46153</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>46153</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46153</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>46153</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>46153</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>46153</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>46153</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>46153</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>46153</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>46153</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>46155</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>46087</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>46092</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>46092</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>46094</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>46094</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>46094</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45077</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>46163</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>46163</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>46163</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>46163</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>46163</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>46163</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>46167</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45940</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46167</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>46167</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>46167</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>46167</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>46167</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>46167</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>46167</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>46167</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>46167</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46167</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>46167</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>46167</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>46169</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>46169</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>46169</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>46170</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>46170</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>46170</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>46170</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38801,7 +38801,7 @@
         <v>46170</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>46170</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>46170</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>46171</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45835</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>45749</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>46175</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39337,7 +39337,7 @@
         <v>46174</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>46175</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>46174</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>46178</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>46181</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>46178</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>46178</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46182</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46182</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>46182</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>46182</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>46183</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>46182</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46181</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>46182</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>46185</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>46187</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46183</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>46186</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>46188</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>46188</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>46191</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>46190</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>46191</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>46195</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>46195</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45947</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>46197</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>46197</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>46203</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>46203</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>46202</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>46202</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>46199</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>46205</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>46203</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>46204</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>46203</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46205</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>46090</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>46205</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>46206</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>46210</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>46212</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>46219</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>46218</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>46266</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>46264</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>46189</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>46223</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>46265</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>46266</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>46265</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>46264</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>46266</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>46223</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>46267</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>46225</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>46268</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>46226</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>46226</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46226</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>46227</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>46227</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>46272</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>46272</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>46269</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>46272</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>46269</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>46272</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>46269</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>46269</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>46186</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>46231</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>46274</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>46273</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>46269</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>46233</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>46232</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>46232</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>46232</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>46233</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>46276</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>46237</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>46234</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>46279</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>46237</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>46233</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>46239</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>46282</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>46239</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>46281</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>46239</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>46240</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>46240</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>46240</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>46286</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46926,7 +46926,7 @@
         <v>46283</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>46241</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>46240</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>46283</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>46283</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>46244</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>46288</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>46245</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>46245</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>46129</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>46244</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>46287</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>46288</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>46244</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>46289</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>46266</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>46246</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>46247</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>46290</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>46247</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>46293</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         <v>46293</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>46293</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>46251</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>46251</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>46251</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>46272</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>46251</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>46252</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>46294</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>46294</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>46251</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>46252</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>46213</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>46254</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>46255</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>46244</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>46255</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>46259</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>46297</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>46259</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>46261</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50167,7 +50167,7 @@
         <v>46304</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>46261</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>46261</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>46261</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>46304</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45973</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>44438</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>44328</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45246</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50937,7 +50937,7 @@
         <v>45247</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45247</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45247</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51171,7 +51171,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>44991</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45247</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45233</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45247</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>45247</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>45687</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45246</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45716</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51868,7 +51868,7 @@
         <v>45995</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>46010</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52024,7 +52024,7 @@
         <v>46036</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>

--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>44489</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>45922</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45289</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44732</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>46199</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>46268</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>46283</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>46258</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44942</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45750</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>44845</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>45054</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45414</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>45328</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>45607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>46203</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46276</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>46239</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>46248</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44959</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45364</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45545</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45075</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45667</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45923</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45726</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45804</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45665</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>45831</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45986</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>44684</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>46120</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44869</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45687</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>46178</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>46199</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>46218</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>46213</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44664</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44505</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44694</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44494</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44655</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>44651</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44719</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44606</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44511</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44713</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44482</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>44783</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44854</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44651</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44518</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44482</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44598</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45203</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45014</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45342</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>45427</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45088</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44579</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45769</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>45401</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45516</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45088</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>45391</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45453</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45096</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>45428</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>45655</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>45230</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45063</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>45037</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45327</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45246</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45208</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>45223</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45471</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45583</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45072</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45408</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45384</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44880</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45700</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>45267</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45245</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45257</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>45418</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>45655</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45204</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>45106</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45195</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44935</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45720</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>45173</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45244</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45271</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>45463</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>45741</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>45133</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>45742</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45628</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45511</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45712</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45077</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>44960</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44957</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45120</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45393</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44980</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45643</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45474</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45740</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>45744</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45902</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45436</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45393</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45524</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45114</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45299</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>44588</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45909</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45567</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>45674</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45418</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45588</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45911</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45495</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>44637</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45471</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45414</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45439</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45439</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45586</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45274</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45664</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>45418</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45484</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>45924</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44672</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45578</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44515</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44508</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>45240</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45790</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45791</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45665</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45477</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45593</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45530</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45925</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45792</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45667</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45439</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44530</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45929</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45322</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44543</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44536</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45796</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>44596</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45747</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45202</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>45618</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45169</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>45793</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45587</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45355</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44515</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45931</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45747</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45579</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>44801</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45933</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>44935</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45658</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45586</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>45063</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45638</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>45805</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>45364</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45805</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45810</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>45470</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45229</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44788</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45469</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45107</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45617</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45567</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45686</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44743</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45826</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45184</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45825</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45700</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45093</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45825</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45826</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45951</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>45827</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45456</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45832</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45951</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45953</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45954</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45959</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45959</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>44691</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45834</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>44998</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45835</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45827</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45159</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45965</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45180</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>45436</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45688</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45965</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45968</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>45968</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>45841</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45971</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45569</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45971</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45972</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45222</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45973</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45167</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45186</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45974</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45974</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45974</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45973</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45750</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45973</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45973</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45973</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45826</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>44803</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45072</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45484</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>44789</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44847</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>44805</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44809</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45245</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45870</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45720</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45087</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>44579</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45982</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45771</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>45882</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45981</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>46094</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>46094</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>46098</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>46098</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45229</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>46100</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45177</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>45985</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>46099</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45700</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>46105</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45750</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45985</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>46107</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44876</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45012</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45988</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>46106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>46107</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>46107</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>46106</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46106</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>46108</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>46108</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>46108</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45229</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45989</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>45992</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>45992</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45992</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>45202</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>45989</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45989</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45989</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45223</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45218</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>46114</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>46119</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>46119</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>46119</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>44887</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>46120</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45993</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>46122</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>44960</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>46122</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>46125</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45996</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45995</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>46127</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45995</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44889</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>46127</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>44951</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>46127</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45995</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>46000</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>46000</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>46001</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>46001</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>46127</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>46127</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>46001</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>46002</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>46126</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>46001</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45152</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>46002</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>46001</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>46129</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>44867</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>46002</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>44911</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>46128</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45568</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45253</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>46001</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>46001</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>46004</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46133</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>46003</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>46134</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>46133</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>46134</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>46134</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>46004</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>46003</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>46006</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>46006</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45232</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>46136</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44994</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>46136</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45153</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>44963</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>46010</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46136</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>46135</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31584,7 +31584,7 @@
         <v>45420</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45896</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>46014</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45758</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45901</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>44872</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45790</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46140</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45819</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44544</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45789</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45114</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45964</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45841</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45986</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32724,7 +32724,7 @@
         <v>44981</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>46040</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45880</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>45841</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45602</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>46140</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>44963</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44805</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>45124</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45124</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33479,7 +33479,7 @@
         <v>44911</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33552,7 +33552,7 @@
         <v>45891</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33630,7 +33630,7 @@
         <v>45835</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46141</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46141</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>45090</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45775</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45939</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>46142</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>45867</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>45834</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>46056</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>46056</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>46142</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45456</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>46059</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>46108</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>46064</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>46148</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46153</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>46153</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46153</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46153</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>46076</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>46153</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>46153</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46153</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>46153</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>46153</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>46153</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>46153</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>46153</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>46153</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>46153</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>46155</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>46087</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>46092</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>46092</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>46094</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>46094</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>46094</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45077</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>46163</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>46163</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>46163</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>46163</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>46163</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>46163</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>46167</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45940</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46167</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>46167</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>46167</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>46167</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>46167</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>46167</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>46167</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>46167</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>46167</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46167</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>46167</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>46167</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>46169</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>46169</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>46169</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>46170</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>46170</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>46170</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>46170</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38801,7 +38801,7 @@
         <v>46170</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>46170</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38957,7 +38957,7 @@
         <v>46170</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>46171</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45835</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>45749</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39259,7 +39259,7 @@
         <v>46175</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39337,7 +39337,7 @@
         <v>46174</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>46175</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>46174</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>46178</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>46181</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>46178</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>46178</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>46182</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46182</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>46182</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>46182</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>46183</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>46182</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>46181</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>46182</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>46185</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>46187</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46183</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>46186</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>46188</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>46188</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>46191</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>46190</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>46191</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>46195</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>46195</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         <v>45947</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>46197</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>46197</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>46203</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>46203</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>46202</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>46202</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>46199</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>46205</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>46203</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>46204</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>46203</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46205</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>46090</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>46205</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>46206</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>46210</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>46212</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>46219</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>46218</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>46266</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>46264</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>46189</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>46223</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>46265</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>46266</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43436,7 +43436,7 @@
         <v>46265</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>46264</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>46266</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>46223</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>46267</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>46225</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>46268</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>46226</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>46226</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46226</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>46227</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>46227</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>46272</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>46272</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>46269</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44601,7 +44601,7 @@
         <v>46272</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>46269</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>46272</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>46269</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44903,7 +44903,7 @@
         <v>46269</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>46186</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>46231</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>46274</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>46273</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>46269</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>46233</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>46232</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>46232</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>46232</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>46233</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45761,7 +45761,7 @@
         <v>46276</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>46237</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>46234</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>46279</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>46237</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>46233</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>46239</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>46282</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>46239</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>46281</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>46239</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>46240</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>46240</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>46240</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>46286</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46926,7 +46926,7 @@
         <v>46283</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>46241</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>46240</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>46283</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>46283</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>46244</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>46288</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>46245</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>46245</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>46129</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>46244</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>46287</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>46288</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>46244</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>46289</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>46266</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>46246</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>46247</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>46290</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>46247</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>46293</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48549,7 +48549,7 @@
         <v>46293</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>46293</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>46251</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>46251</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>46251</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>46272</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>46251</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>46252</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>46294</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>46294</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>46251</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>46252</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>46213</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>46254</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>46255</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>46244</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>46255</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>46259</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>46297</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>46259</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>46261</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50167,7 +50167,7 @@
         <v>46304</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>46261</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>46261</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>46261</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>46304</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45973</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>44438</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>44328</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45246</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50937,7 +50937,7 @@
         <v>45247</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45247</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45247</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51171,7 +51171,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>44991</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45247</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45233</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45247</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>45247</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>45687</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45246</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45716</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51868,7 +51868,7 @@
         <v>45995</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51946,7 +51946,7 @@
         <v>46010</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52024,7 +52024,7 @@
         <v>46036</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>

--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>44489</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>45922</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45289</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44732</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45923</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>46276</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46283</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>46258</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45275</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>46268</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44942</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>44845</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>45607</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45328</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>45750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>46203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>46276</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>46239</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>46248</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45414</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>46308</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>44701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45665</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45545</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45923</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45986</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45687</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>46178</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45364</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>46120</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>46199</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>46218</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>44959</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>44869</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45075</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>46213</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>45195</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45667</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>45726</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45804</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45831</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>44664</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>44606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44505</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44651</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44713</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44783</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44694</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44494</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>44518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44651</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44511</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44655</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44598</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44980</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45674</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44805</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45617</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44637</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45090</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44963</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45218</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45159</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45418</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45578</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45167</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45393</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45742</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45771</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45471</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>44876</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44889</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45223</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45750</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45567</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44963</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45223</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45453</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45587</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45544</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>45153</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>45208</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>45177</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>44935</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45686</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44867</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45245</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45063</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44544</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45643</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>45720</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45107</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>44788</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45427</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45638</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45114</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45896</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45712</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45700</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>46136</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45420</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45245</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>45841</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45790</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45901</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45835</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>46136</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45180</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45072</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>45072</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>46136</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45789</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45271</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>45841</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>45891</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45819</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45169</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>46140</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45939</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45834</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>46140</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>46108</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45867</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>46141</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>45456</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45880</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45775</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45902</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>46141</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45909</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45664</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45911</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>46142</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>46142</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45769</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45246</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45299</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45925</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45924</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>46148</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>45929</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45665</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45124</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>46153</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>46153</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>46153</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>46153</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>46153</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>46153</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45933</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>46153</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>46153</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>46153</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>46153</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>46153</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>46153</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>46153</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>45267</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44508</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>45744</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45253</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45628</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45408</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45951</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>46153</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45087</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45088</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45953</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>46155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45954</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45959</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45959</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45750</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>44911</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>45965</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>45965</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45257</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45093</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45968</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45968</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45971</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45971</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>46163</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45973</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45973</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>45973</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45973</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45972</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>46163</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45436</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>45418</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>45974</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>46163</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45077</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45974</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45974</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>46163</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45974</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>46163</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>46167</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>46167</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45229</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46167</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45393</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45012</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45981</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>46167</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>45982</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45985</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45985</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>46167</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>46167</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45428</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>46167</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>46167</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>46167</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>46167</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>46167</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45988</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45989</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>46167</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45989</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44803</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>46167</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45989</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45364</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45658</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45989</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45992</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45992</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45992</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45993</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>46169</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45995</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45995</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>46169</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45401</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45618</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45995</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45384</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>46169</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45229</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45484</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45327</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45940</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45996</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>46000</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>46001</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>46000</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>45740</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>46001</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>46001</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>46001</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>46170</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>46170</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>46001</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>46001</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46170</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>46170</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>46170</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>46170</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>46170</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>46003</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>46003</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>46001</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45222</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46002</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>46002</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>46174</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46002</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46006</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>46006</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45232</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>46004</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>46004</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>46010</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>46174</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45749</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>46014</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>46171</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45588</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45835</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45391</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44536</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>44579</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45758</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>44911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46175</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45986</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>46175</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>46178</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>46178</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>46040</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45037</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44789</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>46182</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44805</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>46182</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45133</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>46182</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45456</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>46182</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>46182</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>46182</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>46181</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>46181</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>46056</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>46056</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>46183</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>46178</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>46059</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>46183</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44847</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45229</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>46064</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>46188</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>46187</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>46185</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45077</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44960</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>45484</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>46076</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>44588</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>46188</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>46186</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>46190</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45063</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44981</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45203</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45463</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>44579</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>46087</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>46092</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>46191</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>46092</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         <v>46094</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>46191</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>46094</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>46094</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45947</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>46098</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>46098</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>46099</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>46100</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>46195</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45578</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>46195</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45120</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45240</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>46106</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>46106</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>46106</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>46105</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>46107</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>45202</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>46107</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>46107</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>46108</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>46108</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>46197</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>46197</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>46114</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45418</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>46119</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>46119</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>44994</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46119</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>46120</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>46122</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>46202</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45616</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>46125</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>46126</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44887</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45173</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>46129</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>46127</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>46127</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45152</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44951</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>46127</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>46128</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>46199</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>46127</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>46204</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>46133</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>46203</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>46133</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>46203</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>46090</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45014</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44957</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46135</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>46203</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>46134</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>46134</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>46134</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>46199</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>46203</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35340,7 +35340,7 @@
         <v>45474</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>46205</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>46205</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45511</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45964</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44596</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>45186</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>46206</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>46205</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>45569</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>45114</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>45244</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45583</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>46210</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>44691</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45096</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45195</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>46212</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>45655</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>45655</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>46218</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>44935</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>46189</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>46223</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>46223</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>46219</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>46225</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45230</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>46226</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>46226</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>46226</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>46227</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>46272</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46227</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>46273</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>46272</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>46272</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>45274</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>46272</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>46186</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>46232</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45184</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>46274</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>46231</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>46232</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>46232</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>45124</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>46233</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>46276</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45524</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>46279</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>46234</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>46233</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>46237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>46237</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45579</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45568</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>46233</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46281</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>45342</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>46240</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>46283</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>46282</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>46239</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>46239</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>46240</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>46239</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>46283</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>46240</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>46240</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>46287</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>46286</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>46129</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46244</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>45567</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>46244</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>45700</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>46245</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>46241</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>46244</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>46283</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45088</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>46289</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>46245</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>46288</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>46246</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44530</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45439</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>46288</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>44960</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45436</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>46290</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>46247</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>46247</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44880</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45700</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45204</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>45720</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>46293</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>46293</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>46293</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>46252</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>44872</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>46251</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>45516</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>46252</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43443,7 +43443,7 @@
         <v>46294</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>44809</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43594,7 +43594,7 @@
         <v>46251</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44672</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44998</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>46294</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>46251</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>46251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>46251</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>46272</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45741</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>46244</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>46254</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>46213</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44510,7 +44510,7 @@
         <v>46255</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>45471</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44666,7 +44666,7 @@
         <v>45414</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>46255</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45586</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45495</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>45439</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>46297</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>44515</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45477</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45530</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>45791</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>45593</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>46259</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>45790</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46259</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45667</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45793</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45792</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>46304</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>46261</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45355</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>44543</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>45747</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>44515</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>46261</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45796</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45439</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45931</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>46202</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>45322</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>46094</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>46261</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45747</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45973</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>44801</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>46304</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47326,7 +47326,7 @@
         <v>46108</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>46261</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45602</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45586</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47633,7 +47633,7 @@
         <v>46265</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45805</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47779,7 +47779,7 @@
         <v>45805</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>46267</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>46266</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>46265</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>46264</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>46266</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>46266</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>46266</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>46264</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>46308</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45810</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45470</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>45469</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>46269</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>46268</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>46269</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>46269</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>46269</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45825</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>45825</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>46311</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>46269</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45826</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45827</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45832</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>45835</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45834</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49855,7 +49855,7 @@
         <v>45827</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45688</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>45841</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>45826</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45870</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45882</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>44438</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>44328</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         <v>45247</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50547,7 +50547,7 @@
         <v>45246</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>45247</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45247</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50937,7 +50937,7 @@
         <v>44991</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>45247</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45233</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51166,7 +51166,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51244,7 +51244,7 @@
         <v>45247</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45687</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45246</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45716</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>45995</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>46010</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>46036</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>

--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>44489</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>45922</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>46255</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45680</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45289</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44732</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45923</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>46199</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>46276</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>46283</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>46258</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45275</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>46268</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44942</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>44845</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>45607</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45328</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>45750</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>46203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>46276</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>46239</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>46248</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45414</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>46308</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>44505</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44503</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>44701</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44684</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45665</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45545</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>45923</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45986</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45687</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>46178</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>45364</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>46120</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>46199</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>46218</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>44959</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>44869</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45075</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>46213</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>45195</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45667</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>45726</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45804</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>45831</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45691</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44613</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>44664</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>44606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>44746</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44726</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>44505</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44651</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44713</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44783</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44694</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
         <v>44494</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>44518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44651</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44511</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44655</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44598</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44980</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45674</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44805</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45617</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44637</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45090</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44963</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45218</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45159</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45418</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45578</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44743</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45167</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45393</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45742</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45771</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45471</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>44876</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44889</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45223</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45750</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45567</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44963</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45223</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45453</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45587</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45544</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>45153</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>45208</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>45177</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>44935</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45686</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>44867</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45245</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45063</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44544</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45643</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45106</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>45720</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>45107</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>44788</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45427</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45638</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45114</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45896</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45712</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45700</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>46136</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45420</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45245</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>45841</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45790</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45901</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45835</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>46136</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45180</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45072</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>45072</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>46136</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45789</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45271</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>45841</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>45891</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45819</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45169</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>46140</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45939</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45834</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>46140</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>46108</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45867</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>46141</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>45456</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45880</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45775</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45902</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>46141</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45909</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45664</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45911</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>46142</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>46142</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45769</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45246</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45299</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45925</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45924</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>46148</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>45929</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45665</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45124</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>46153</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>46153</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>46153</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>46153</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>46153</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>46153</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45933</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>46153</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>46153</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>46153</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>46153</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>46153</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>46153</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>46153</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>45267</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44508</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>45744</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45253</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45628</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45408</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45951</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>46153</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45087</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45088</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45953</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>46155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45954</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45959</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45959</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45750</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>44911</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>45965</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>45965</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45257</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45093</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45968</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45968</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45971</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45971</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>46163</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45973</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45973</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>45973</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45973</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45972</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>46163</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45436</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>45418</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>45974</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>46163</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45077</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45974</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45974</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>46163</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45974</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>46163</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>46167</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>46167</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45229</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46167</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45393</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45012</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45981</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>46167</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>45982</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45985</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45985</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>46167</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>46167</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45428</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>46167</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>46167</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>46167</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>46167</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>46167</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45988</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45989</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>46167</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45989</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44803</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>46167</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45989</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45364</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45658</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45989</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45992</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45992</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45992</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45993</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>46169</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45995</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45995</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>46169</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45401</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45618</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45995</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45384</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>46169</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45229</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45484</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45327</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45940</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45996</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>46000</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>46001</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>46000</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>45740</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>46001</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>46001</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>46001</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>46170</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>46170</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>46001</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>46001</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46170</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>46170</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>46170</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>46170</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>46170</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>46003</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>46003</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>46001</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45222</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46002</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>46002</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>46174</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46002</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46006</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>46006</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45232</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>46004</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>46004</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>46010</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>46174</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45749</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25921,7 +25921,7 @@
         <v>46014</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>46171</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45588</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>45835</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>45391</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44536</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>44579</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45758</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>44911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46175</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45986</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>46175</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>46178</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>46178</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>46040</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45037</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44789</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>46182</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44805</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>45202</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>46182</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45133</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>46182</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45456</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>46182</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>46182</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>46182</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>46181</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>46181</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>46056</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>46056</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>46183</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>46178</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>46059</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>46183</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44847</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45229</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>46064</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>46188</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>46187</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>46185</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45077</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44960</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>45484</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>46076</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>44588</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>46188</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>46186</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>46190</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>45063</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>44981</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45203</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45463</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>44579</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>46087</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>46092</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>46191</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>46092</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         <v>46094</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>46191</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>46094</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>46094</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45947</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>46098</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>46098</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>46099</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>46100</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>46195</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45578</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>46195</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45120</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45240</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>46106</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>46106</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>46106</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>46105</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>46107</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>45202</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>46107</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>46107</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>46108</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>46108</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>46197</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>46197</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>46114</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45418</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>46119</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>46119</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>44994</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46119</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>46120</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>46122</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>46202</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45616</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>46125</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33176,7 +33176,7 @@
         <v>46126</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44887</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45173</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>46129</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>46127</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>46127</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45152</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44951</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>46127</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>46128</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34029,7 +34029,7 @@
         <v>46199</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>46127</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>46204</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>46133</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>46203</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>46133</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>46203</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>46090</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45014</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44957</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46135</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>46203</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>46134</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>46134</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>46134</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>46199</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>46203</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35340,7 +35340,7 @@
         <v>45474</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>46205</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>46205</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45511</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45964</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44596</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>45186</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>46206</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>46205</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>45569</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>45114</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>45244</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45583</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>46210</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>44691</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45096</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45195</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>46212</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>45655</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>45655</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>46218</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>44935</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>46189</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>46223</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>46223</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>46219</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>46225</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45230</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>46226</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>46226</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>46226</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>46227</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>46272</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>46227</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>46273</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38000,7 +38000,7 @@
         <v>46272</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>46272</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>45274</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>46272</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38297,7 +38297,7 @@
         <v>46186</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>46232</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45184</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>46274</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>46231</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>46232</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>46232</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>45124</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>46233</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>46276</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45524</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39145,7 +39145,7 @@
         <v>46279</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>46234</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>46233</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>46237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>46237</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45579</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45568</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>46233</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46281</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>45342</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>46240</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>46283</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>46282</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>46239</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>46239</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>46240</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>46239</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>46283</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>46240</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>46240</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>46287</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>46286</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>46129</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46244</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>45567</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>46244</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>45700</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>46245</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>46241</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>46244</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>46283</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45088</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>46289</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>46245</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>46288</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>46246</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44530</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45439</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>46288</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>44960</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45436</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>46290</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>46247</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>46247</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44880</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42605,7 +42605,7 @@
         <v>45700</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45204</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>45720</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>46293</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>46293</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>46293</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>46252</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>44872</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>46251</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>45516</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>46252</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43443,7 +43443,7 @@
         <v>46294</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>44809</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43594,7 +43594,7 @@
         <v>46251</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44672</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44998</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>46294</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>46251</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>46251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>46251</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         <v>46272</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45741</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>46244</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>46254</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44437,7 +44437,7 @@
         <v>46213</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44510,7 +44510,7 @@
         <v>46255</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>45471</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44666,7 +44666,7 @@
         <v>45414</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>46255</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45586</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45495</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>45439</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>46297</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>44515</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45477</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>45530</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>45791</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>45593</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>46259</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>45790</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>46259</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45667</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45793</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45792</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>46304</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>46261</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45355</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>44543</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>45747</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>44515</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>46261</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45796</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>45439</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45931</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>46202</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>45322</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>46094</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>46261</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47024,7 +47024,7 @@
         <v>45747</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45973</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>44801</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>46304</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47326,7 +47326,7 @@
         <v>46108</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>46261</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45602</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45586</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47633,7 +47633,7 @@
         <v>46265</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45805</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47779,7 +47779,7 @@
         <v>45805</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>46267</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>46266</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>46265</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>46264</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>46266</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>46266</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>46266</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>46264</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>46308</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45810</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45470</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>45469</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>46269</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>46268</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>46269</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>46269</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>46269</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45825</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>45825</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>46311</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>46269</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45826</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45827</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45832</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>45835</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45834</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49855,7 +49855,7 @@
         <v>45827</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45688</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>45841</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>45826</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45870</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45882</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>44438</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>44328</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         <v>45247</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50547,7 +50547,7 @@
         <v>45246</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>45247</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45247</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>45247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50937,7 +50937,7 @@
         <v>44991</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>45247</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45233</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51166,7 +51166,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51244,7 +51244,7 @@
         <v>45247</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>45687</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>45246</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45716</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>45995</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>46010</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>46036</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>

--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>45922</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>46182</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45680</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45289</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>44732</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>45183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45923</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>46199</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45275</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46283</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>46258</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>46268</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44942</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>46239</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45054</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>45414</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>46248</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44845</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>46308</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>46276</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45328</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>44505</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>44503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>44701</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>45364</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>45923</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>44959</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>46178</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>46199</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>45986</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>46218</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45667</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45687</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45726</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>45804</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45545</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>46213</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45831</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>46120</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>45075</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45195</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44684</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>45665</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44578</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45691</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44613</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44664</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44606</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44746</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44505</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44651</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44719</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44606</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>44713</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44783</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>44799</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44694</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44494</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44651</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44511</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44655</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>44598</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45230</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>45246</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>44994</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45153</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>44963</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45203</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45342</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45909</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45077</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45911</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46163</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44544</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>46163</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>46163</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>46163</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>46163</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45114</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>46167</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45940</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46167</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>46167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>46167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>45924</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44981</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>46167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>46167</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>46167</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>46167</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>46167</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>46167</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>46167</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>46167</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>46169</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45925</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>46169</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>46169</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>46170</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>46170</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>46170</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>46170</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>46170</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45929</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>46170</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>46170</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>46171</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45835</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44963</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45749</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44805</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>45124</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45124</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44911</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45933</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45090</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>46175</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>46174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45391</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45453</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>46175</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45096</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>46174</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45428</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44579</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>45208</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45223</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>45471</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45401</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45408</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45384</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44880</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>46178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>45516</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>46181</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>46178</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>45655</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45037</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45951</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>46178</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45951</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>46182</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>46182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45953</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>46182</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45327</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>46182</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45954</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>46183</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>46182</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>46181</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>46182</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>46185</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45578</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45583</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>46187</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>46183</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>45959</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>46186</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45072</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45959</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>46188</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45267</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>46188</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45965</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>46191</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45965</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>46190</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45968</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45968</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>46191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>46195</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>46195</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45257</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45418</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45971</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45655</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45971</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45972</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45947</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45204</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45973</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>46197</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45195</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>46197</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45974</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45974</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45973</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44935</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45973</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45973</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45973</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45720</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45173</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>46199</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>46203</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>46203</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46202</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45742</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45628</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>46199</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>45982</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>46205</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>46203</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45981</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45712</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>46204</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45077</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46203</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45985</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>46205</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>46090</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>46205</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45985</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45988</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45643</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>45740</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>46206</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45989</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45992</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45744</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45992</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45989</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>46210</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45989</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45989</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45993</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>46212</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45996</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45436</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45995</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45995</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45995</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45524</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>45299</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46219</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>46000</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>46218</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>46000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>46001</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>46001</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>46001</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>46189</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>46002</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>46223</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>46001</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>46002</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>46001</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>46002</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>46223</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>46001</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>46225</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>46001</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>46004</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>46003</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>46226</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>46226</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>46226</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>46227</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46227</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>46004</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>46003</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>46006</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>46006</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45495</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>46186</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>46231</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45471</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45414</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45232</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>46233</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>46232</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>46232</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>46232</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>46233</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>46010</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45439</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>46237</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>46234</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45586</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>46014</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>46279</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>46237</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>46233</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45244</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45758</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46239</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>46239</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44515</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45790</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>46281</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>46239</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45791</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46240</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45477</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45593</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45530</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>46240</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46240</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>46286</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45792</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>46283</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>46241</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>45463</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45667</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>45439</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45322</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>44543</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45796</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>46240</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45986</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>46283</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45747</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>46283</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>46244</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>46288</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45793</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>46040</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45355</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>46245</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>46245</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>44515</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45747</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>46129</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>46244</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>46287</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44801</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>46288</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>46244</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>46289</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45586</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>46246</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>46056</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>46056</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
         <v>45805</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>45805</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45810</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45470</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>46247</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>46290</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>46247</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>46059</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>46293</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>46293</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45469</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>46293</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>46064</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45511</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>46076</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>46251</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>46251</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>46251</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45826</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45825</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>46251</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45825</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>46252</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>46294</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>46294</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>46251</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45827</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>45832</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>46252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>46213</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45834</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>46087</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45835</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>46254</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>45827</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>46092</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45688</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>46092</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>46094</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>46094</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>46094</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>46098</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>46098</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45841</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45120</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>46255</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>46244</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>46255</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>46100</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>46099</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>46105</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45474</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46259</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>46107</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45826</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>46106</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>46107</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>46107</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>46106</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>46106</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>46297</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>46108</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>46108</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>46259</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>46261</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>46114</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>46119</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>46119</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>46119</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45870</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>46120</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>46122</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>46125</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>46304</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>46261</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>46127</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>46261</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>46127</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>44951</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>46127</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>46127</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>46127</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>46261</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>46304</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>46126</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45152</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45393</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45973</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>46129</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45602</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>46128</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>46094</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>46264</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>46264</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>45882</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>46265</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>46133</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>46134</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>46133</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>46134</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>46134</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>44588</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>46108</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45674</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>46308</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>46136</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46202</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45931</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>46136</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>46266</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>46266</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>46136</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>46135</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45420</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>46266</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45896</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>45901</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>45664</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>46266</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>46269</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>46311</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>46268</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45790</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45418</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46269</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>46140</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45819</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>44672</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>46269</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45578</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45789</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>46269</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>45240</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>46269</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>46267</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>45964</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45841</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>46272</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45880</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45841</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>46273</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>46140</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>46272</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>44530</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45891</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>46272</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45202</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>46272</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>46272</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45587</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45835</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>46141</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>46141</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>46274</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45579</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45775</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45939</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>46142</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41857,7 +41857,7 @@
         <v>45867</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>45834</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>46142</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45456</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>44935</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>46108</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46276</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>46148</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45364</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>46153</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>46153</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>46153</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>46153</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>46153</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42929,7 +42929,7 @@
         <v>46153</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>46153</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>44788</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>46153</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>46153</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>46153</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>46153</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>46153</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>46153</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>46153</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>46155</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>45617</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45567</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>44998</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45436</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45569</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45072</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44245,7 +44245,7 @@
         <v>45484</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45720</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>44579</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45771</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45229</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>45700</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45750</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>45012</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45202</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45014</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45427</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45088</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>45167</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>45769</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>45088</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45063</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45245</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45106</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45271</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45741</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45133</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>44960</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>44957</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>45393</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>44980</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45544</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45114</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>45567</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>45616</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46447,7 +46447,7 @@
         <v>45418</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45588</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>44637</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45439</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45671</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45274</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45484</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>44508</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45665</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>44536</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>44596</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>45618</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45169</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45658</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45063</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45638</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45229</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45107</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45686</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>44743</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45184</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45700</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>45093</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48171,7 +48171,7 @@
         <v>45456</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>44691</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45159</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45180</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45222</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45167</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>45186</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>45750</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44803</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>44789</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>44847</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>44805</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>44809</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>45245</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45087</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45177</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>44876</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>45229</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45223</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45218</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>44887</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>44960</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>44889</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>44867</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>44911</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50056,7 +50056,7 @@
         <v>45568</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>45253</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>44438</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>44328</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>45247</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50431,7 +50431,7 @@
         <v>45246</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50509,7 +50509,7 @@
         <v>45247</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45247</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50665,7 +50665,7 @@
         <v>45247</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50821,7 +50821,7 @@
         <v>44991</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50894,7 +50894,7 @@
         <v>45247</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50972,7 +50972,7 @@
         <v>45233</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45247</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         <v>45687</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45246</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>45716</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45995</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51518,7 +51518,7 @@
         <v>46010</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51596,7 +51596,7 @@
         <v>46036</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>

--- a/Översikt FILIPSTAD.xlsx
+++ b/Översikt FILIPSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>43936</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45551</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>45922</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>46182</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>45980</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>45680</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45289</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>44732</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>45183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45923</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>46199</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45275</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46283</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>46258</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>46268</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44942</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45750</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>46239</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45054</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>45414</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>46248</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44845</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>46308</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>46276</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45328</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>44505</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>44503</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>44701</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>45364</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>45923</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>44959</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>46178</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>46199</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>45986</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>46218</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45667</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45687</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45726</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>45804</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45545</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>46213</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45831</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>46120</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>45075</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>45195</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>44684</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>45665</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44578</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45691</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44613</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44664</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44606</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44746</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44505</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44651</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44719</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44606</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>44713</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44783</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>44799</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44854</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44694</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44494</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44651</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44511</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44655</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>44598</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45230</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>45246</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>44994</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45153</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>44963</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45203</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>45342</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45909</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45077</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>45911</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>46163</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44544</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>46163</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>46163</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>46163</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>46163</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45114</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>46167</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45940</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>46167</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>46167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>46167</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>45924</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44981</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>46167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>46167</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>46167</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>46167</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>46167</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>46167</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>46167</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>46167</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>46169</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45925</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>46169</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>46169</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>46170</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>46170</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>46170</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>46170</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>46170</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45929</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>46170</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>46170</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>46171</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>45835</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44963</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45749</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44805</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>45124</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45124</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44911</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45933</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45090</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>46175</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>46174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45391</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45453</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>46175</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45096</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>46174</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45428</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44579</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>45208</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45223</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>45471</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45401</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45408</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45384</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44880</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>46178</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>45516</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>46181</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>46178</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>45655</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45037</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45951</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>46178</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45951</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>46182</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>46182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45953</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>46182</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45327</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>46182</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45954</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>46183</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>46182</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>46181</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>46182</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>46185</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45578</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45583</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15666,7 +15666,7 @@
         <v>46187</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>46183</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>45959</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>46186</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45072</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45959</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>46188</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>45267</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>46188</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45965</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>46191</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45965</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>46190</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45968</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45968</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>46191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>46195</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>46195</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45257</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45418</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45971</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45655</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45971</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45972</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45947</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45204</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45973</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>46197</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45195</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>46197</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45974</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45974</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>45974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45973</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44935</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45973</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45973</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45973</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45720</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45173</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>46199</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>46203</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>46203</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46202</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45742</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45628</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>46199</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>45982</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>46205</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>46203</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45981</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45712</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>46204</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45077</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46203</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45985</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>46205</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>46090</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>46205</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45985</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45988</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45643</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>45740</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>46206</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45989</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45992</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45744</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45992</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45989</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>46210</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45989</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45989</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45993</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>46212</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45996</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45436</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45995</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45995</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45995</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45524</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>45299</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46219</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>46000</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>46218</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>46000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>46001</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>46001</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>46001</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>46189</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>46002</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>46223</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>46001</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>46002</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>46001</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>46002</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>46223</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>46001</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>46225</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>46001</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>46004</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>46003</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>46226</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>46226</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>46226</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>46227</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46227</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>46004</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>46003</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>46006</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>46006</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45495</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>46186</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>46231</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>45471</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>45414</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>45232</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>46233</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>46232</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>46232</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>46232</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>46233</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>46010</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45439</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>46237</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>46234</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45586</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>46014</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>46279</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>46237</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>46233</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45244</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45758</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46239</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>46239</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44515</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45790</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>46281</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>46239</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45791</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46240</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45477</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45593</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45530</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>46240</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46240</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>46286</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45792</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>46283</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>46241</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>45463</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45667</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>45439</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45322</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>44543</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45796</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>46240</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45986</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>46283</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45747</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>46283</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>46244</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>46288</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45793</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>46040</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45355</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>46245</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>46245</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>44515</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45747</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>46129</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>46244</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>46287</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44801</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>46288</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>46244</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>46289</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45586</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>46246</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>46056</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>46056</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
         <v>45805</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>45805</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45810</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45470</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>46247</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>46290</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>46247</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>46059</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>46293</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>46293</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45469</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>46293</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>46064</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45511</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>46076</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>46251</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>46251</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>46251</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31014,7 +31014,7 @@
         <v>45826</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45825</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>46251</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45825</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>46252</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>46294</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>46294</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>46251</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45827</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>45832</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>46252</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>46213</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45834</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>46087</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45835</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>46254</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>45827</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>46092</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>45688</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>46092</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>46094</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>46094</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>46094</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>46098</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>46098</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45841</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45120</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>46255</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>46244</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>46255</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>46100</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>46099</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>46105</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45474</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>46259</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>46107</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45826</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>46106</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>46107</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>46107</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>46106</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>46106</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>46297</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>46108</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>46108</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>46259</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>46261</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>46114</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>46119</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>46119</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         <v>46119</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45870</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35020,7 +35020,7 @@
         <v>46120</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>46122</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>46125</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>46304</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>46261</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>46127</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>46261</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>46127</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>44951</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         <v>46127</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>46127</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>46127</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>46261</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>46304</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>46126</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45152</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45393</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45973</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>46129</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>45602</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>46128</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>46265</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>46094</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>46264</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>46264</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>45882</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>46265</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>46133</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>46134</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>46133</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>46134</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>46134</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>44588</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>46108</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45674</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>46308</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>46136</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46202</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45931</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>46136</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>46266</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>46266</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>46136</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>46135</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45420</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>46266</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45896</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>45901</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38724,7 +38724,7 @@
         <v>45664</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>46266</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>46269</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>46311</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>46268</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45790</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>45418</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46269</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>46140</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45819</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>44672</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>46269</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45578</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45789</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>46269</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>45240</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>46269</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>46267</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>45964</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45841</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>46272</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45880</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>45841</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>46273</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>46140</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>46272</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>44530</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45891</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>46272</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>45202</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>46272</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>46272</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45587</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45835</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>46141</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>46141</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>46274</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45579</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45775</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45939</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>46142</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41857,7 +41857,7 @@
         <v>45867</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>45834</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>46142</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45456</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>44935</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>46108</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46276</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>46148</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45364</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>46153</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>46153</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>46153</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>46153</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>46153</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42929,7 +42929,7 @@
         <v>46153</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>46153</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>44788</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>46153</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>46153</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>46153</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>46153</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>46153</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43548,7 +43548,7 @@
         <v>46153</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>46153</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>46155</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>45617</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45567</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>44998</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45436</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45569</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45072</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44245,7 +44245,7 @@
         <v>45484</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45720</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>44579</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45771</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44547,7 +44547,7 @@
         <v>45229</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44620,7 +44620,7 @@
         <v>45700</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45750</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>45012</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45202</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45014</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45427</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45088</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>45167</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>45769</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>45088</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45063</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45245</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45106</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45271</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45741</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45133</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>44960</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>44957</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>45393</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>44980</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45544</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45114</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>45567</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>45616</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46447,7 +46447,7 @@
         <v>45418</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45588</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>44637</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45439</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45671</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45274</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45484</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>44508</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>45665</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>44536</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>44596</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>45618</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45169</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45658</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45063</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45638</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45229</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45107</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45686</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>44743</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45184</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45700</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>45093</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48171,7 +48171,7 @@
         <v>45456</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>44691</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45159</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45180</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45222</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45167</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>45186</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>45750</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>44803</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>44789</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>44847</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>44805</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>44809</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>45245</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45087</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45177</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>44876</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>45229</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45223</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45218</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>44887</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>44960</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>44889</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>44867</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>44911</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50056,7 +50056,7 @@
         <v>45568</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>45253</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>44438</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>44328</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>45247</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50431,7 +50431,7 @@
         <v>45246</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50509,7 +50509,7 @@
         <v>45247</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45247</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50665,7 +50665,7 @@
         <v>45247</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>45247</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50821,7 +50821,7 @@
         <v>44991</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50894,7 +50894,7 @@
         <v>45247</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50972,7 +50972,7 @@
         <v>45233</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45247</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45247</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         <v>45687</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45246</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>45716</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45995</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51518,7 +51518,7 @@
         <v>46010</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51596,7 +51596,7 @@
         <v>46036</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
